--- a/data/trans_bre/P15B_tráfico-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P15B_tráfico-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-5,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,33%</t>
+          <t>-18,22%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 40,01</t>
+          <t>-18,03; 42,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 40,01</t>
+          <t>-19,09; 40,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -0,65</t>
+          <t>-45,58; 0,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 19,23</t>
+          <t>-28,21; 16,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 386,17</t>
+          <t>-66,49; 351,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 193,82</t>
+          <t>-68,55; 121,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,15</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,0%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,29; 91,85</t>
+          <t>31,04; 87,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 25,11</t>
+          <t>-27,47; 25,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 19,06</t>
+          <t>-38,63; 20,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 16,68</t>
+          <t>-34,3; 23,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,53; 579,26</t>
+          <t>42,45; 571,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 112,79</t>
+          <t>-62,33; 106,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,61; 187,1</t>
+          <t>-85,5; 209,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 80,91</t>
+          <t>-63,02; 130,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-24,18</t>
+          <t>-20,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-65,47%</t>
+          <t>-60,1%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,28; -2,79</t>
+          <t>-22,69; -2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 26,57</t>
+          <t>-24,14; 34,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 57,63</t>
+          <t>-13,78; 52,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 0,34</t>
+          <t>-41,18; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 145,52</t>
+          <t>-77,77; 169,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 894,35</t>
+          <t>-100,0; 1168,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,21; 26,81</t>
+          <t>-100,0; 23,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-2,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,69%</t>
+          <t>-12,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 8,41</t>
+          <t>-39,0; 9,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 13,38</t>
+          <t>-15,4; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 14,58</t>
+          <t>-21,71; 14,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 15,48</t>
+          <t>-20,11; 13,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,53; 32,53</t>
+          <t>-78,25; 36,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 86,44</t>
+          <t>-58,73; 79,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,86; 71,82</t>
+          <t>-59,71; 73,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 135,39</t>
+          <t>-63,44; 99,43</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-66,6; -0,8</t>
+          <t>-63,93; 1,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 8,22</t>
+          <t>-23,57; 10,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 10,67</t>
+          <t>-17,72; 10,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 19,06</t>
+          <t>-15,59; 20,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,82; 13,42</t>
+          <t>-88,31; -0,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 75,23</t>
+          <t>-72,94; 90,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 163,15</t>
+          <t>-78,06; 191,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 243,13</t>
+          <t>-57,74; 268,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-20,72</t>
+          <t>-18,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,13%</t>
+          <t>-46,53%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,21; -14,25</t>
+          <t>-67,92; -15,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,69; -1,62</t>
+          <t>-35,79; -1,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 15,52</t>
+          <t>-20,38; 13,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,15; 25,28</t>
+          <t>-66,59; 21,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,03</t>
+          <t>-100,0; -41,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,05; -3,78</t>
+          <t>-82,9; -6,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-67,49; 279,71</t>
+          <t>-72,63; 201,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-92,35; 2109,91</t>
+          <t>-87,47; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-5,58</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-19,73%</t>
+          <t>-20,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 0,48</t>
+          <t>-23,79; 0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,56</t>
+          <t>-13,44; 0,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 3,31</t>
+          <t>-12,87; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 4,47</t>
+          <t>-14,48; 3,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 5,19</t>
+          <t>-61,34; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 2,71</t>
+          <t>-47,42; 2,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,23; 21,07</t>
+          <t>-48,94; 16,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 24,12</t>
+          <t>-45,94; 15,02</t>
         </is>
       </c>
     </row>
